--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5306-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5306-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D85E68C9-671D-489E-A21A-4C4D132894F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{282A3A40-FF58-4E29-92A8-B59DF24BE47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{63965915-ADA6-4B0D-8534-1D9CD1DCEEE8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C3652B8C-5A5A-46DD-B811-3DCBEF53E00D}"/>
   </bookViews>
   <sheets>
     <sheet name="5306-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1576,25 +1576,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBE7245B-2FEA-4F41-93FC-40B018C08317}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460F6A5C-7168-4E71-A4A4-6849AEF5884B}">
   <dimension ref="A1:R59"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1622,7 +1622,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1748,7 +1748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1828,7 +1828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51">
         <v>2020</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="49">
         <v>2019</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2018</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="49">
         <v>2017</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="51">
         <v>2016</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="49">
         <v>2015</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="51">
         <v>2014</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2013</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="51">
         <v>2012</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="49">
         <v>2011</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="51">
         <v>2010</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="49">
         <v>2009</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2008</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="49">
         <v>2007</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="51">
         <v>2006</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="49">
         <v>2005</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="51">
         <v>2004</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="49">
         <v>2003</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="51">
         <v>2002</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="49">
         <v>2001</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="51">
         <v>2000</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="49">
         <v>1999</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="51">
         <v>1998</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="49">
         <v>1997</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="51">
         <v>1996</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="49">
         <v>1995</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="51">
         <v>1994</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="49">
         <v>1993</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="51" t="s">
         <v>63</v>
       </c>
